--- a/#Covid19_anonymized.xlsx
+++ b/#Covid19_anonymized.xlsx
@@ -520,7 +520,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>负面</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
@@ -564,7 +564,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>负面</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
@@ -608,7 +608,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>负面</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
@@ -652,7 +652,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>负面</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
@@ -696,7 +696,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>负面</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
@@ -7979,7 +7979,7 @@
       </c>
       <c r="J190" t="inlineStr">
         <is>
-          <t>负面</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
@@ -8021,7 +8021,7 @@
       </c>
       <c r="J191" t="inlineStr">
         <is>
-          <t>负面</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
@@ -8063,7 +8063,7 @@
       </c>
       <c r="J192" t="inlineStr">
         <is>
-          <t>负面</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
@@ -8105,7 +8105,7 @@
       </c>
       <c r="J193" t="inlineStr">
         <is>
-          <t>负面</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
@@ -8148,7 +8148,7 @@
       </c>
       <c r="J194" t="inlineStr">
         <is>
-          <t>负面</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
@@ -8191,7 +8191,7 @@
       </c>
       <c r="J195" t="inlineStr">
         <is>
-          <t>负面</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
@@ -13136,7 +13136,7 @@
       </c>
       <c r="J343" t="inlineStr">
         <is>
-          <t>负面</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
@@ -18587,7 +18587,7 @@
       </c>
       <c r="J501" t="inlineStr">
         <is>
-          <t>负面</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
@@ -18629,7 +18629,7 @@
       </c>
       <c r="J502" t="inlineStr">
         <is>
-          <t>负面</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
@@ -18673,7 +18673,7 @@
       </c>
       <c r="J503" t="inlineStr">
         <is>
-          <t>负面</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
@@ -18715,7 +18715,7 @@
       </c>
       <c r="J504" t="inlineStr">
         <is>
-          <t>负面</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
@@ -18757,7 +18757,7 @@
       </c>
       <c r="J505" t="inlineStr">
         <is>
-          <t>负面</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
@@ -18801,7 +18801,7 @@
       </c>
       <c r="J506" t="inlineStr">
         <is>
-          <t>负面</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
@@ -18843,7 +18843,7 @@
       </c>
       <c r="J507" t="inlineStr">
         <is>
-          <t>负面</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
